--- a/Sun Pharmaceutical.xlsx
+++ b/Sun Pharmaceutical.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7C7E5C5-062F-4B15-84FF-3F320A1ABE4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F6245B-EA8C-4C24-B764-A857AD0F8EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35970" yWindow="0" windowWidth="35025" windowHeight="20160" xr2:uid="{2804E39D-5296-473D-A17D-443404DD5D3E}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="19050" windowHeight="16100" xr2:uid="{2804E39D-5296-473D-A17D-443404DD5D3E}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -153,9 +153,6 @@
     <t>EV INR</t>
   </si>
   <si>
-    <t>Q224</t>
-  </si>
-  <si>
     <t>FY23</t>
   </si>
   <si>
@@ -172,6 +169,9 @@
   </si>
   <si>
     <t>deuruxolitinib</t>
+  </si>
+  <si>
+    <t>Q126</t>
   </si>
 </sst>
 </file>
@@ -609,23 +609,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7877BF51-3531-4F8B-B54C-DB136B4A1D0F}">
   <dimension ref="B2:K7"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="10" max="10" width="10.85546875" customWidth="1"/>
+    <col min="10" max="10" width="10.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I2" t="s">
         <v>0</v>
       </c>
       <c r="J2" s="1">
-        <v>1815.95</v>
-      </c>
-    </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I3" t="s">
         <v>1</v>
       </c>
@@ -633,49 +633,49 @@
         <v>2399</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I4" t="s">
         <v>2</v>
       </c>
       <c r="J4" s="1">
         <f>+J2*J3</f>
-        <v>4356464.05</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+        <v>4591686</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I5" t="s">
         <v>3</v>
       </c>
       <c r="J5" s="1">
-        <f>7695.5+68.8+33869+520.4+123985.8+245.1</f>
-        <v>166384.6</v>
+        <f>37890.7+17.6+666.1+209334.5+97705.1+527+14036.9</f>
+        <v>360177.9</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I6" t="s">
         <v>4</v>
       </c>
       <c r="J6" s="1">
-        <f>110360.1+704.6+25491.2</f>
-        <v>136555.90000000002</v>
+        <f>40503.5+25721.8+6307.9</f>
+        <v>72533.2</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I7" t="s">
         <v>37</v>
       </c>
       <c r="J7" s="1">
         <f>+J4-J5+J6</f>
-        <v>4326635.3499999996</v>
+        <v>4304041.3</v>
       </c>
     </row>
   </sheetData>
@@ -686,24 +686,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E53269B-2360-4737-9277-78EB0C000931}">
   <dimension ref="A1:AA17"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" customWidth="1"/>
-    <col min="3" max="14" width="9.140625" style="2"/>
+    <col min="2" max="2" width="14.26953125" customWidth="1"/>
+    <col min="3" max="14" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="AA2" s="6">
         <v>45382</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
@@ -771,13 +771,13 @@
         <v>36</v>
       </c>
       <c r="Z3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AA3" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:27" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
@@ -833,7 +833,7 @@
         <v>498510.4</v>
       </c>
     </row>
-    <row r="5" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>19</v>
       </c>
@@ -863,7 +863,7 @@
         <v>106626.1</v>
       </c>
     </row>
-    <row r="6" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>20</v>
       </c>
@@ -893,7 +893,7 @@
         <v>391884.30000000005</v>
       </c>
     </row>
-    <row r="7" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>21</v>
       </c>
@@ -923,7 +923,7 @@
         <v>248472.4</v>
       </c>
     </row>
-    <row r="8" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
@@ -953,7 +953,7 @@
         <v>143411.90000000005</v>
       </c>
     </row>
-    <row r="9" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>23</v>
       </c>
@@ -979,7 +979,7 @@
         <v>2384.6999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>24</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>141027.20000000004</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>25</v>
       </c>
@@ -1035,7 +1035,7 @@
         <v>14394.5</v>
       </c>
     </row>
-    <row r="12" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>26</v>
       </c>
@@ -1065,9 +1065,9 @@
         <v>126632.70000000004</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Z15" s="1">
         <v>49593.3</v>
@@ -1076,9 +1076,9 @@
         <v>121349.8</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Z16" s="1">
         <v>20855.8</v>
@@ -1087,9 +1087,9 @@
         <v>22018.1</v>
       </c>
     </row>
-    <row r="17" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Z17" s="1">
         <f>+Z15-Z16</f>
